--- a/v05.xlsx
+++ b/v05.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\f8589383-a06a-42d4-bc9a-5d085d6d4735\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\20440a04-be79-459e-8694-4ca4e8928dda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C04848D4-CC9F-4776-81C1-4B0298F85C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{017BB5ED-AD98-458F-9275-52F57A7A1416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C105" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440"/>

--- a/v05.xlsx
+++ b/v05.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\20440a04-be79-459e-8694-4ca4e8928dda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\5db62f64-5236-44b3-9594-a491814e1c69\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{017BB5ED-AD98-458F-9275-52F57A7A1416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8EC8281-390A-491F-B3C4-EA64642BFF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C105" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440"/>

--- a/v05.xlsx
+++ b/v05.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\5db62f64-5236-44b3-9594-a491814e1c69\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\c64a08cf-893c-48b4-adf6-cbb69641e99b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8EC8281-390A-491F-B3C4-EA64642BFF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86915A46-F1A4-4C22-8BA7-9633DBFF71D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C105" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440"/>
